--- a/ETF Summary Report.xlsx
+++ b/ETF Summary Report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Documents/Ventures/Hemrek Capital/Investment/ETF/Samhita/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F481225-6341-7D42-BB2A-58F83D3FBF8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55649C8E-56D8-4649-A36D-753529B57ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manthan" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Manthan!$B$1:$F$31</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +31,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -325,248 +324,547 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Watchlist"/>
+      <sheetName val="Portfolio Summary Report"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="2">
-          <cell r="B2" t="str">
-            <v>AUTOIETF</v>
-          </cell>
-          <cell r="D2" t="str">
-            <v>28.08</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>BANKIETF</v>
-          </cell>
-          <cell r="D3" t="str">
-            <v>60.21</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4" t="str">
-            <v>COMMOIETF</v>
-          </cell>
-          <cell r="D4" t="str">
-            <v>94.25</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5" t="str">
-            <v>CONSUMIETF</v>
-          </cell>
-          <cell r="D5" t="str">
-            <v>128.07</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6" t="str">
-            <v>CPSEETF</v>
-          </cell>
-          <cell r="D6" t="str">
-            <v>93.09</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7" t="str">
-            <v>ECAPINSURE</v>
-          </cell>
-          <cell r="D7" t="str">
-            <v>24.19</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8" t="str">
-            <v>EVINDIA</v>
-          </cell>
-          <cell r="D8" t="str">
-            <v>31.30</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9" t="str">
-            <v>FINIETF</v>
-          </cell>
-          <cell r="D9" t="str">
-            <v>32.41</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10" t="str">
-            <v>FMCGIETF</v>
-          </cell>
-          <cell r="D10" t="str">
-            <v>59.13</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="B11" t="str">
-            <v>GOLDIETF</v>
-          </cell>
-          <cell r="D11" t="str">
-            <v>104.16</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="B12" t="str">
-            <v>HEALTHIETF</v>
-          </cell>
-          <cell r="D12" t="str">
-            <v>151.63</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="B13" t="str">
-            <v>INFRAIETF</v>
-          </cell>
-          <cell r="D13" t="str">
-            <v>98.93</v>
-          </cell>
-        </row>
         <row r="14">
           <cell r="B14" t="str">
-            <v>ITIETF</v>
-          </cell>
-          <cell r="D14" t="str">
-            <v>39.45</v>
+            <v>Allcargo Logistics</v>
+          </cell>
+          <cell r="C14">
+            <v>501</v>
+          </cell>
+          <cell r="D14">
+            <v>60.14</v>
           </cell>
         </row>
         <row r="15">
           <cell r="B15" t="str">
-            <v>MAKEINDIA</v>
-          </cell>
-          <cell r="D15" t="str">
-            <v>155.32</v>
+            <v>Baid Finserv</v>
+          </cell>
+          <cell r="C15">
+            <v>1500</v>
+          </cell>
+          <cell r="D15">
+            <v>14.83</v>
           </cell>
         </row>
         <row r="16">
           <cell r="B16" t="str">
-            <v>MASPTOP50</v>
-          </cell>
-          <cell r="D16" t="str">
-            <v>68.88</v>
+            <v>Bandhan Bank</v>
+          </cell>
+          <cell r="C16">
+            <v>315</v>
+          </cell>
+          <cell r="D16">
+            <v>183.23</v>
           </cell>
         </row>
         <row r="17">
           <cell r="B17" t="str">
-            <v>METALIETF</v>
-          </cell>
-          <cell r="D17" t="str">
-            <v>10.44</v>
+            <v>CPSE ETF</v>
+          </cell>
+          <cell r="C17">
+            <v>350</v>
+          </cell>
+          <cell r="D17">
+            <v>83.77</v>
           </cell>
         </row>
         <row r="18">
           <cell r="B18" t="str">
-            <v>MIDCAPIETF</v>
-          </cell>
-          <cell r="D18" t="str">
-            <v>22.99</v>
+            <v>Edelweiss BSE Capital Markets &amp; Insurance ETF</v>
+          </cell>
+          <cell r="C18">
+            <v>922</v>
+          </cell>
+          <cell r="D18">
+            <v>21.46</v>
           </cell>
         </row>
         <row r="19">
           <cell r="B19" t="str">
-            <v>MNC</v>
-          </cell>
-          <cell r="D19" t="str">
-            <v>30.82</v>
+            <v>ESAF Small Finance Bank</v>
+          </cell>
+          <cell r="C19">
+            <v>4648</v>
+          </cell>
+          <cell r="D19">
+            <v>47.86</v>
           </cell>
         </row>
         <row r="20">
           <cell r="B20" t="str">
-            <v>MODEFENCE</v>
-          </cell>
-          <cell r="D20" t="str">
-            <v>90.40</v>
+            <v>ICICI Bank</v>
+          </cell>
+          <cell r="C20">
+            <v>180</v>
+          </cell>
+          <cell r="D20">
+            <v>355.6</v>
           </cell>
         </row>
         <row r="21">
           <cell r="B21" t="str">
-            <v>MON100</v>
-          </cell>
-          <cell r="D21" t="str">
-            <v>234.28</v>
+            <v>ICICI Prudential BSE Sensex ETF</v>
+          </cell>
+          <cell r="C21">
+            <v>43</v>
+          </cell>
+          <cell r="D21">
+            <v>868.84</v>
           </cell>
         </row>
         <row r="22">
           <cell r="B22" t="str">
-            <v>MONIFTY500</v>
-          </cell>
-          <cell r="D22" t="str">
-            <v>24.24</v>
+            <v>ICICI Prudential Gold ETF</v>
+          </cell>
+          <cell r="C22">
+            <v>114</v>
+          </cell>
+          <cell r="D22">
+            <v>84.69</v>
           </cell>
         </row>
         <row r="23">
           <cell r="B23" t="str">
-            <v>MOREALTY</v>
-          </cell>
-          <cell r="D23" t="str">
-            <v>92.88</v>
+            <v>ICICI Prudential Nifty 50 ETF</v>
+          </cell>
+          <cell r="C23">
+            <v>129</v>
+          </cell>
+          <cell r="D23">
+            <v>261.92</v>
           </cell>
         </row>
         <row r="24">
           <cell r="B24" t="str">
-            <v>MOSMALL250</v>
-          </cell>
-          <cell r="D24" t="str">
-            <v>17.11</v>
+            <v>ICICI Prudential Nifty Auto ETF</v>
+          </cell>
+          <cell r="C24">
+            <v>2310</v>
+          </cell>
+          <cell r="D24">
+            <v>22.6</v>
           </cell>
         </row>
         <row r="25">
           <cell r="B25" t="str">
-            <v>NIFTYIETF</v>
-          </cell>
-          <cell r="D25" t="str">
-            <v>291.44</v>
+            <v>ICICI Prudential Nifty Bank ETF</v>
+          </cell>
+          <cell r="C25">
+            <v>795</v>
+          </cell>
+          <cell r="D25">
+            <v>51.43</v>
           </cell>
         </row>
         <row r="26">
           <cell r="B26" t="str">
-            <v>OILIETF</v>
-          </cell>
-          <cell r="D26" t="str">
-            <v>12.35</v>
+            <v>ICICI Prudential Nifty Commodities ETF</v>
+          </cell>
+          <cell r="C26">
+            <v>480</v>
+          </cell>
+          <cell r="D26">
+            <v>80.8</v>
           </cell>
         </row>
         <row r="27">
           <cell r="B27" t="str">
-            <v>PSUBNKIETF</v>
-          </cell>
-          <cell r="D27" t="str">
-            <v>85.85</v>
+            <v>ICICI Prudential Nifty Consumption ETF</v>
+          </cell>
+          <cell r="C27">
+            <v>355</v>
+          </cell>
+          <cell r="D27">
+            <v>112.89</v>
           </cell>
         </row>
         <row r="28">
           <cell r="B28" t="str">
-            <v>PVTBANIETF</v>
-          </cell>
-          <cell r="D28" t="str">
-            <v>28.59</v>
+            <v>ICICI Prudential Nifty Financial Serv. Ex-Bank ETF</v>
+          </cell>
+          <cell r="C28">
+            <v>1568</v>
+          </cell>
+          <cell r="D28">
+            <v>25.92</v>
           </cell>
         </row>
         <row r="29">
           <cell r="B29" t="str">
-            <v>SENSEXIETF</v>
-          </cell>
-          <cell r="D29" t="str">
-            <v>967.96</v>
+            <v>ICICI Prudential Nifty FMCG ETF</v>
+          </cell>
+          <cell r="C29">
+            <v>387</v>
+          </cell>
+          <cell r="D29">
+            <v>56.9</v>
           </cell>
         </row>
         <row r="30">
           <cell r="B30" t="str">
-            <v>SILVERIETF</v>
-          </cell>
-          <cell r="D30" t="str">
-            <v>152.56</v>
+            <v>ICICI Prudential Nifty Healthcare ETF</v>
+          </cell>
+          <cell r="C30">
+            <v>133</v>
+          </cell>
+          <cell r="D30">
+            <v>138.41999999999999</v>
           </cell>
         </row>
         <row r="31">
           <cell r="B31" t="str">
-            <v>TNIDETF</v>
-          </cell>
-          <cell r="D31" t="str">
-            <v>96.83</v>
+            <v>ICICI Prudential Nifty Infrastructure ETF</v>
+          </cell>
+          <cell r="C31">
+            <v>504</v>
+          </cell>
+          <cell r="D31">
+            <v>85.73</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="B32" t="str">
+            <v>ICICI Prudential Nifty IT ETF</v>
+          </cell>
+          <cell r="C32">
+            <v>989</v>
+          </cell>
+          <cell r="D32">
+            <v>38.26</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="B33" t="str">
+            <v>ICICI Prudential Nifty Metal ETF</v>
+          </cell>
+          <cell r="C33">
+            <v>2116</v>
+          </cell>
+          <cell r="D33">
+            <v>9.07</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="B34" t="str">
+            <v>ICICI Prudential Nifty Midcap 150 ETF</v>
+          </cell>
+          <cell r="C34">
+            <v>2148</v>
+          </cell>
+          <cell r="D34">
+            <v>20.07</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="B35" t="str">
+            <v>ICICI Prudential Nifty Oil &amp; Gas ETF</v>
+          </cell>
+          <cell r="C35">
+            <v>3401</v>
+          </cell>
+          <cell r="D35">
+            <v>10.87</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="B36" t="str">
+            <v>ICICI Prudential Nifty Private Bank ETF</v>
+          </cell>
+          <cell r="C36">
+            <v>1719</v>
+          </cell>
+          <cell r="D36">
+            <v>25.27</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="B37" t="str">
+            <v>ICICI Prudential Nifty PSU Bank ETF</v>
+          </cell>
+          <cell r="C37">
+            <v>671</v>
+          </cell>
+          <cell r="D37">
+            <v>62.6</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="B38" t="str">
+            <v>ICICI Prudential Silver ETF</v>
+          </cell>
+          <cell r="C38">
+            <v>103</v>
+          </cell>
+          <cell r="D38">
+            <v>103.31</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="B39" t="str">
+            <v>Indian Railway Finance Corporation</v>
+          </cell>
+          <cell r="C39">
+            <v>2000</v>
+          </cell>
+          <cell r="D39">
+            <v>25.38</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="B40" t="str">
+            <v>Kotak Nifty MNC ETF</v>
+          </cell>
+          <cell r="C40">
+            <v>1988</v>
+          </cell>
+          <cell r="D40">
+            <v>27.37</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="B41" t="str">
+            <v>Kotak Nifty PSU Bank ETF</v>
+          </cell>
+          <cell r="C41">
+            <v>11</v>
+          </cell>
+          <cell r="D41">
+            <v>672.24</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="B42" t="str">
+            <v>Life Insurance Corporation of India (LIC)</v>
+          </cell>
+          <cell r="C42">
+            <v>15</v>
+          </cell>
+          <cell r="D42">
+            <v>949</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="B43" t="str">
+            <v>Mirae Asset Nifty EV and New Age Automotive ETF</v>
+          </cell>
+          <cell r="C43">
+            <v>1359</v>
+          </cell>
+          <cell r="D43">
+            <v>27.37</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="B44" t="str">
+            <v>Mirae Asset Nifty India Manufacturing ETF</v>
+          </cell>
+          <cell r="C44">
+            <v>252</v>
+          </cell>
+          <cell r="D44">
+            <v>131.75</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="B45" t="str">
+            <v>Mirae Asset Nifty Midcap 150 ETF</v>
+          </cell>
+          <cell r="C45">
+            <v>128</v>
+          </cell>
+          <cell r="D45">
+            <v>19.809999999999999</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="B46" t="str">
+            <v>Mirae Asset S&amp;P 500 Top 50 ETF</v>
+          </cell>
+          <cell r="C46">
+            <v>385</v>
+          </cell>
+          <cell r="D46">
+            <v>49.51</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="B47" t="str">
+            <v>Motherson Sumi Wiring India</v>
+          </cell>
+          <cell r="C47">
+            <v>237</v>
+          </cell>
+          <cell r="D47">
+            <v>9.1199999999999992</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="B48" t="str">
+            <v>Motilal Oswal MOSt Shares NASDAQ-100 ETF</v>
+          </cell>
+          <cell r="C48">
+            <v>220</v>
+          </cell>
+          <cell r="D48">
+            <v>174.53</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="B49" t="str">
+            <v>Motilal Oswal Nifty 100 ETF</v>
+          </cell>
+          <cell r="C49">
+            <v>36</v>
+          </cell>
+          <cell r="D49">
+            <v>26.68</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="B50" t="str">
+            <v>Motilal Oswal Nifty 500 ETF</v>
+          </cell>
+          <cell r="C50">
+            <v>1679</v>
+          </cell>
+          <cell r="D50">
+            <v>22</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="B51" t="str">
+            <v>Motilal Oswal Nifty India Defence ETF</v>
+          </cell>
+          <cell r="C51">
+            <v>314</v>
+          </cell>
+          <cell r="D51">
+            <v>69.650000000000006</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="B52" t="str">
+            <v>Motilal Oswal Nifty Realty ETF</v>
+          </cell>
+          <cell r="C52">
+            <v>383</v>
+          </cell>
+          <cell r="D52">
+            <v>85.75</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="B53" t="str">
+            <v>Motilal Oswal Nifty Smallcap 250</v>
+          </cell>
+          <cell r="C53">
+            <v>1649</v>
+          </cell>
+          <cell r="D53">
+            <v>15.62</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="B54" t="str">
+            <v>Nippon India NIFTY Pharma ETF Growth Plan</v>
+          </cell>
+          <cell r="C54">
+            <v>50</v>
+          </cell>
+          <cell r="D54">
+            <v>21.39</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="B55" t="str">
+            <v>Olectra Greentech</v>
+          </cell>
+          <cell r="C55">
+            <v>200</v>
+          </cell>
+          <cell r="D55">
+            <v>134.61000000000001</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="B56" t="str">
+            <v>ONGC Limited</v>
+          </cell>
+          <cell r="C56">
+            <v>276</v>
+          </cell>
+          <cell r="D56">
+            <v>231.96</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="B57" t="str">
+            <v>SBI Cards &amp; Payment Services</v>
+          </cell>
+          <cell r="C57">
+            <v>19</v>
+          </cell>
+          <cell r="D57">
+            <v>836.75</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="B58" t="str">
+            <v>Spandana Sphoorty Financial</v>
+          </cell>
+          <cell r="C58">
+            <v>521</v>
+          </cell>
+          <cell r="D58">
+            <v>690.09</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="B59" t="str">
+            <v>Tata Nifty India Digital ETF</v>
+          </cell>
+          <cell r="C59">
+            <v>508</v>
+          </cell>
+          <cell r="D59">
+            <v>86.35</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="B60" t="str">
+            <v>TruCap Finance</v>
+          </cell>
+          <cell r="C60">
+            <v>600</v>
+          </cell>
+          <cell r="D60">
+            <v>49.01</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="B61" t="str">
+            <v>Utkarsh Small Finance Bank</v>
+          </cell>
+          <cell r="C61">
+            <v>7303</v>
+          </cell>
+          <cell r="D61">
+            <v>42.58</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="B62" t="str">
+            <v>Yes Bank</v>
+          </cell>
+          <cell r="C62">
+            <v>2147</v>
+          </cell>
+          <cell r="D62">
+            <v>22.4</v>
           </cell>
         </row>
       </sheetData>
@@ -582,547 +880,248 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Portfolio Summary Report"/>
+      <sheetName val="Watchlist"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
+        <row r="2">
+          <cell r="B2" t="str">
+            <v>AUTOIETF</v>
+          </cell>
+          <cell r="D2" t="str">
+            <v>28.08</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>BANKIETF</v>
+          </cell>
+          <cell r="D3" t="str">
+            <v>60.21</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="B4" t="str">
+            <v>COMMOIETF</v>
+          </cell>
+          <cell r="D4" t="str">
+            <v>94.25</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="B5" t="str">
+            <v>CONSUMIETF</v>
+          </cell>
+          <cell r="D5" t="str">
+            <v>128.07</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="B6" t="str">
+            <v>CPSEETF</v>
+          </cell>
+          <cell r="D6" t="str">
+            <v>93.09</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="B7" t="str">
+            <v>ECAPINSURE</v>
+          </cell>
+          <cell r="D7" t="str">
+            <v>24.19</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="B8" t="str">
+            <v>EVINDIA</v>
+          </cell>
+          <cell r="D8" t="str">
+            <v>31.30</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="B9" t="str">
+            <v>FINIETF</v>
+          </cell>
+          <cell r="D9" t="str">
+            <v>32.41</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="B10" t="str">
+            <v>FMCGIETF</v>
+          </cell>
+          <cell r="D10" t="str">
+            <v>59.13</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="B11" t="str">
+            <v>GOLDIETF</v>
+          </cell>
+          <cell r="D11" t="str">
+            <v>104.16</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="B12" t="str">
+            <v>HEALTHIETF</v>
+          </cell>
+          <cell r="D12" t="str">
+            <v>151.63</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="B13" t="str">
+            <v>INFRAIETF</v>
+          </cell>
+          <cell r="D13" t="str">
+            <v>98.93</v>
+          </cell>
+        </row>
         <row r="14">
           <cell r="B14" t="str">
-            <v>Allcargo Logistics</v>
-          </cell>
-          <cell r="C14">
-            <v>501</v>
-          </cell>
-          <cell r="D14">
-            <v>60.14</v>
+            <v>ITIETF</v>
+          </cell>
+          <cell r="D14" t="str">
+            <v>39.45</v>
           </cell>
         </row>
         <row r="15">
           <cell r="B15" t="str">
-            <v>Baid Finserv</v>
-          </cell>
-          <cell r="C15">
-            <v>1500</v>
-          </cell>
-          <cell r="D15">
-            <v>14.83</v>
+            <v>MAKEINDIA</v>
+          </cell>
+          <cell r="D15" t="str">
+            <v>155.32</v>
           </cell>
         </row>
         <row r="16">
           <cell r="B16" t="str">
-            <v>Bandhan Bank</v>
-          </cell>
-          <cell r="C16">
-            <v>315</v>
-          </cell>
-          <cell r="D16">
-            <v>183.23</v>
+            <v>MASPTOP50</v>
+          </cell>
+          <cell r="D16" t="str">
+            <v>68.88</v>
           </cell>
         </row>
         <row r="17">
           <cell r="B17" t="str">
-            <v>CPSE ETF</v>
-          </cell>
-          <cell r="C17">
-            <v>346</v>
-          </cell>
-          <cell r="D17">
-            <v>83.68</v>
+            <v>METALIETF</v>
+          </cell>
+          <cell r="D17" t="str">
+            <v>10.44</v>
           </cell>
         </row>
         <row r="18">
           <cell r="B18" t="str">
-            <v>Edelweiss BSE Capital Markets &amp; Insurance ETF</v>
-          </cell>
-          <cell r="C18">
-            <v>813</v>
-          </cell>
-          <cell r="D18">
-            <v>21.11</v>
+            <v>MIDCAPIETF</v>
+          </cell>
+          <cell r="D18" t="str">
+            <v>22.99</v>
           </cell>
         </row>
         <row r="19">
           <cell r="B19" t="str">
-            <v>ESAF Small Finance Bank</v>
-          </cell>
-          <cell r="C19">
-            <v>4648</v>
-          </cell>
-          <cell r="D19">
-            <v>47.86</v>
+            <v>MNC</v>
+          </cell>
+          <cell r="D19" t="str">
+            <v>30.82</v>
           </cell>
         </row>
         <row r="20">
           <cell r="B20" t="str">
-            <v>ICICI Bank</v>
-          </cell>
-          <cell r="C20">
-            <v>180</v>
-          </cell>
-          <cell r="D20">
-            <v>355.6</v>
+            <v>MODEFENCE</v>
+          </cell>
+          <cell r="D20" t="str">
+            <v>90.40</v>
           </cell>
         </row>
         <row r="21">
           <cell r="B21" t="str">
-            <v>ICICI Prudential BSE Sensex ETF</v>
-          </cell>
-          <cell r="C21">
-            <v>41</v>
-          </cell>
-          <cell r="D21">
-            <v>863.71</v>
+            <v>MON100</v>
+          </cell>
+          <cell r="D21" t="str">
+            <v>234.28</v>
           </cell>
         </row>
         <row r="22">
           <cell r="B22" t="str">
-            <v>ICICI Prudential Gold ETF</v>
-          </cell>
-          <cell r="C22">
-            <v>109</v>
-          </cell>
-          <cell r="D22">
-            <v>83.72</v>
+            <v>MONIFTY500</v>
+          </cell>
+          <cell r="D22" t="str">
+            <v>24.24</v>
           </cell>
         </row>
         <row r="23">
           <cell r="B23" t="str">
-            <v>ICICI Prudential Nifty 50 ETF</v>
-          </cell>
-          <cell r="C23">
-            <v>115</v>
-          </cell>
-          <cell r="D23">
-            <v>258.17</v>
+            <v>MOREALTY</v>
+          </cell>
+          <cell r="D23" t="str">
+            <v>92.88</v>
           </cell>
         </row>
         <row r="24">
           <cell r="B24" t="str">
-            <v>ICICI Prudential Nifty Auto ETF</v>
-          </cell>
-          <cell r="C24">
-            <v>2220</v>
-          </cell>
-          <cell r="D24">
-            <v>22.37</v>
+            <v>MOSMALL250</v>
+          </cell>
+          <cell r="D24" t="str">
+            <v>17.11</v>
           </cell>
         </row>
         <row r="25">
           <cell r="B25" t="str">
-            <v>ICICI Prudential Nifty Bank ETF</v>
-          </cell>
-          <cell r="C25">
-            <v>732</v>
-          </cell>
-          <cell r="D25">
-            <v>50.66</v>
+            <v>NIFTYIETF</v>
+          </cell>
+          <cell r="D25" t="str">
+            <v>291.44</v>
           </cell>
         </row>
         <row r="26">
           <cell r="B26" t="str">
-            <v>ICICI Prudential Nifty Commodities ETF</v>
-          </cell>
-          <cell r="C26">
-            <v>476</v>
-          </cell>
-          <cell r="D26">
-            <v>80.709999999999994</v>
+            <v>OILIETF</v>
+          </cell>
+          <cell r="D26" t="str">
+            <v>12.35</v>
           </cell>
         </row>
         <row r="27">
           <cell r="B27" t="str">
-            <v>ICICI Prudential Nifty Consumption ETF</v>
-          </cell>
-          <cell r="C27">
-            <v>337</v>
-          </cell>
-          <cell r="D27">
-            <v>112.06</v>
+            <v>PSUBNKIETF</v>
+          </cell>
+          <cell r="D27" t="str">
+            <v>85.85</v>
           </cell>
         </row>
         <row r="28">
           <cell r="B28" t="str">
-            <v>ICICI Prudential Nifty Financial Serv. Ex-Bank ETF</v>
-          </cell>
-          <cell r="C28">
-            <v>1549</v>
-          </cell>
-          <cell r="D28">
-            <v>25.85</v>
+            <v>PVTBANIETF</v>
+          </cell>
+          <cell r="D28" t="str">
+            <v>28.59</v>
           </cell>
         </row>
         <row r="29">
           <cell r="B29" t="str">
-            <v>ICICI Prudential Nifty FMCG ETF</v>
-          </cell>
-          <cell r="C29">
-            <v>381</v>
-          </cell>
-          <cell r="D29">
-            <v>56.87</v>
+            <v>SENSEXIETF</v>
+          </cell>
+          <cell r="D29" t="str">
+            <v>967.96</v>
           </cell>
         </row>
         <row r="30">
           <cell r="B30" t="str">
-            <v>ICICI Prudential Nifty Healthcare ETF</v>
-          </cell>
-          <cell r="C30">
-            <v>129</v>
-          </cell>
-          <cell r="D30">
-            <v>138.02000000000001</v>
+            <v>SILVERIETF</v>
+          </cell>
+          <cell r="D30" t="str">
+            <v>152.56</v>
           </cell>
         </row>
         <row r="31">
           <cell r="B31" t="str">
-            <v>ICICI Prudential Nifty Infrastructure ETF</v>
-          </cell>
-          <cell r="C31">
-            <v>463</v>
-          </cell>
-          <cell r="D31">
-            <v>84.58</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="B32" t="str">
-            <v>ICICI Prudential Nifty IT ETF</v>
-          </cell>
-          <cell r="C32">
-            <v>935</v>
-          </cell>
-          <cell r="D32">
-            <v>38.119999999999997</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="B33" t="str">
-            <v>ICICI Prudential Nifty Metal ETF</v>
-          </cell>
-          <cell r="C33">
-            <v>2075</v>
-          </cell>
-          <cell r="D33">
-            <v>9.0399999999999991</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="B34" t="str">
-            <v>ICICI Prudential Nifty Midcap 150 ETF</v>
-          </cell>
-          <cell r="C34">
-            <v>2129</v>
-          </cell>
-          <cell r="D34">
-            <v>20.04</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="B35" t="str">
-            <v>ICICI Prudential Nifty Oil &amp; Gas ETF</v>
-          </cell>
-          <cell r="C35">
-            <v>3306</v>
-          </cell>
-          <cell r="D35">
-            <v>10.83</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="B36" t="str">
-            <v>ICICI Prudential Nifty Private Bank ETF</v>
-          </cell>
-          <cell r="C36">
-            <v>1623</v>
-          </cell>
-          <cell r="D36">
-            <v>25.07</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="B37" t="str">
-            <v>ICICI Prudential Nifty PSU Bank ETF</v>
-          </cell>
-          <cell r="C37">
-            <v>652</v>
-          </cell>
-          <cell r="D37">
-            <v>61.96</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="B38" t="str">
-            <v>ICICI Prudential Silver ETF</v>
-          </cell>
-          <cell r="C38">
-            <v>99</v>
-          </cell>
-          <cell r="D38">
-            <v>101.28</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="B39" t="str">
-            <v>Indian Railway Finance Corporation</v>
-          </cell>
-          <cell r="C39">
-            <v>2000</v>
-          </cell>
-          <cell r="D39">
-            <v>25.38</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="B40" t="str">
-            <v>Kotak Nifty MNC ETF</v>
-          </cell>
-          <cell r="C40">
-            <v>1975</v>
-          </cell>
-          <cell r="D40">
-            <v>27.34</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="B41" t="str">
-            <v>Kotak Nifty PSU Bank ETF</v>
-          </cell>
-          <cell r="C41">
-            <v>11</v>
-          </cell>
-          <cell r="D41">
-            <v>672.24</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="B42" t="str">
-            <v>Life Insurance Corporation of India (LIC)</v>
-          </cell>
-          <cell r="C42">
-            <v>15</v>
-          </cell>
-          <cell r="D42">
-            <v>949</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="B43" t="str">
-            <v>Mirae Asset Nifty EV and New Age Automotive ETF</v>
-          </cell>
-          <cell r="C43">
-            <v>1322</v>
-          </cell>
-          <cell r="D43">
-            <v>27.27</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="B44" t="str">
-            <v>Mirae Asset Nifty India Manufacturing ETF</v>
-          </cell>
-          <cell r="C44">
-            <v>249</v>
-          </cell>
-          <cell r="D44">
-            <v>131.49</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="B45" t="str">
-            <v>Mirae Asset Nifty Midcap 150 ETF</v>
-          </cell>
-          <cell r="C45">
-            <v>128</v>
-          </cell>
-          <cell r="D45">
-            <v>19.809999999999999</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="B46" t="str">
-            <v>Mirae Asset S&amp;P 500 Top 50 ETF</v>
-          </cell>
-          <cell r="C46">
-            <v>380</v>
-          </cell>
-          <cell r="D46">
-            <v>49.28</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="B47" t="str">
-            <v>Motherson Sumi Wiring India</v>
-          </cell>
-          <cell r="C47">
-            <v>237</v>
-          </cell>
-          <cell r="D47">
-            <v>9.1199999999999992</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="B48" t="str">
-            <v>Motilal Oswal MOSt Shares NASDAQ-100 ETF</v>
-          </cell>
-          <cell r="C48">
-            <v>218</v>
-          </cell>
-          <cell r="D48">
-            <v>174.02</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="B49" t="str">
-            <v>Motilal Oswal Nifty 500 ETF</v>
-          </cell>
-          <cell r="C49">
-            <v>1553</v>
-          </cell>
-          <cell r="D49">
-            <v>21.83</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="B50" t="str">
-            <v>Motilal Oswal Nifty India Defence ETF</v>
-          </cell>
-          <cell r="C50">
-            <v>310</v>
-          </cell>
-          <cell r="D50">
-            <v>69.430000000000007</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="B51" t="str">
-            <v>Motilal Oswal Nifty Realty ETF</v>
-          </cell>
-          <cell r="C51">
-            <v>379</v>
-          </cell>
-          <cell r="D51">
-            <v>85.71</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="B52" t="str">
-            <v>Motilal Oswal Nifty Smallcap 250</v>
-          </cell>
-          <cell r="C52">
-            <v>1625</v>
-          </cell>
-          <cell r="D52">
-            <v>15.6</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="B53" t="str">
-            <v>Nippon India NIFTY Pharma ETF Growth Plan</v>
-          </cell>
-          <cell r="C53">
-            <v>50</v>
-          </cell>
-          <cell r="D53">
-            <v>21.39</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="B54" t="str">
-            <v>Olectra Greentech</v>
-          </cell>
-          <cell r="C54">
-            <v>200</v>
-          </cell>
-          <cell r="D54">
-            <v>134.61000000000001</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="B55" t="str">
-            <v>ONGC Limited</v>
-          </cell>
-          <cell r="C55">
-            <v>276</v>
-          </cell>
-          <cell r="D55">
-            <v>231.96</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="B56" t="str">
-            <v>SBI Cards &amp; Payment Services</v>
-          </cell>
-          <cell r="C56">
-            <v>19</v>
-          </cell>
-          <cell r="D56">
-            <v>836.75</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="B57" t="str">
-            <v>Spandana Sphoorty Financial</v>
-          </cell>
-          <cell r="C57">
-            <v>521</v>
-          </cell>
-          <cell r="D57">
-            <v>690.09</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="B58" t="str">
-            <v>Take Solutions</v>
-          </cell>
-          <cell r="C58">
-            <v>2200</v>
-          </cell>
-          <cell r="D58">
-            <v>18.97</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="B59" t="str">
-            <v>Tata Nifty India Digital ETF</v>
-          </cell>
-          <cell r="C59">
-            <v>502</v>
-          </cell>
-          <cell r="D59">
-            <v>86.21</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="B60" t="str">
-            <v>TruCap Finance</v>
-          </cell>
-          <cell r="C60">
-            <v>600</v>
-          </cell>
-          <cell r="D60">
-            <v>49.01</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="B61" t="str">
-            <v>Utkarsh Small Finance Bank</v>
-          </cell>
-          <cell r="C61">
-            <v>7303</v>
-          </cell>
-          <cell r="D61">
-            <v>42.58</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="B62" t="str">
-            <v>Yes Bank</v>
-          </cell>
-          <cell r="C62">
-            <v>2147</v>
-          </cell>
-          <cell r="D62">
-            <v>22.4</v>
+            <v>TNIDETF</v>
+          </cell>
+          <cell r="D31" t="str">
+            <v>96.83</v>
           </cell>
         </row>
       </sheetData>
@@ -1132,9 +1131,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1172,7 +1171,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1278,7 +1277,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1420,7 +1419,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1466,15 +1465,15 @@
         <v>34</v>
       </c>
       <c r="D2" s="3">
-        <f>LOOKUP(B2,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>2220</v>
+        <f>LOOKUP(B2,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>2310</v>
       </c>
       <c r="E2" s="3">
-        <f>LOOKUP(B2,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>22.37</v>
+        <f>LOOKUP(B2,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>22.6</v>
       </c>
       <c r="F2" s="3" t="str">
-        <f>LOOKUP(C2,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C2,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>28.08</v>
       </c>
     </row>
@@ -1489,15 +1488,15 @@
         <v>35</v>
       </c>
       <c r="D3" s="3">
-        <f>LOOKUP(B3,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>732</v>
+        <f>LOOKUP(B3,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>795</v>
       </c>
       <c r="E3" s="3">
-        <f>LOOKUP(B3,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>50.66</v>
+        <f>LOOKUP(B3,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>51.43</v>
       </c>
       <c r="F3" s="3" t="str">
-        <f>LOOKUP(C3,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C3,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>60.21</v>
       </c>
     </row>
@@ -1512,15 +1511,15 @@
         <v>39</v>
       </c>
       <c r="D4" s="3">
-        <f>LOOKUP(B4,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>476</v>
+        <f>LOOKUP(B4,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>480</v>
       </c>
       <c r="E4" s="3">
-        <f>LOOKUP(B4,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>80.709999999999994</v>
+        <f>LOOKUP(B4,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>80.8</v>
       </c>
       <c r="F4" s="3" t="str">
-        <f>LOOKUP(C4,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C4,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>94.25</v>
       </c>
     </row>
@@ -1535,15 +1534,15 @@
         <v>42</v>
       </c>
       <c r="D5" s="3">
-        <f>LOOKUP(B5,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>337</v>
+        <f>LOOKUP(B5,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>355</v>
       </c>
       <c r="E5" s="3">
-        <f>LOOKUP(B5,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>112.06</v>
+        <f>LOOKUP(B5,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>112.89</v>
       </c>
       <c r="F5" s="3" t="str">
-        <f>LOOKUP(C5,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C5,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>128.07</v>
       </c>
     </row>
@@ -1558,15 +1557,15 @@
         <v>65</v>
       </c>
       <c r="D6" s="3">
-        <f>LOOKUP(B6,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>346</v>
+        <f>LOOKUP(B6,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>350</v>
       </c>
       <c r="E6" s="3">
-        <f>LOOKUP(B6,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>83.68</v>
+        <f>LOOKUP(B6,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>83.77</v>
       </c>
       <c r="F6" s="3" t="str">
-        <f>LOOKUP(C6,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C6,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>93.09</v>
       </c>
     </row>
@@ -1581,15 +1580,15 @@
         <v>58</v>
       </c>
       <c r="D7" s="3">
-        <f>LOOKUP(B7,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>813</v>
+        <f>LOOKUP(B7,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>922</v>
       </c>
       <c r="E7" s="3">
-        <f>LOOKUP(B7,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>21.11</v>
+        <f>LOOKUP(B7,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>21.46</v>
       </c>
       <c r="F7" s="3" t="str">
-        <f>LOOKUP(C7,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C7,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>24.19</v>
       </c>
     </row>
@@ -1604,15 +1603,15 @@
         <v>51</v>
       </c>
       <c r="D8" s="3">
-        <f>LOOKUP(B8,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>1322</v>
+        <f>LOOKUP(B8,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>1359</v>
       </c>
       <c r="E8" s="3">
-        <f>LOOKUP(B8,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>27.27</v>
+        <f>LOOKUP(B8,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>27.37</v>
       </c>
       <c r="F8" s="3" t="str">
-        <f>LOOKUP(C8,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C8,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>31.30</v>
       </c>
     </row>
@@ -1627,15 +1626,15 @@
         <v>43</v>
       </c>
       <c r="D9" s="3">
-        <f>LOOKUP(B9,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>1549</v>
+        <f>LOOKUP(B9,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>1568</v>
       </c>
       <c r="E9" s="3">
-        <f>LOOKUP(B9,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>25.85</v>
+        <f>LOOKUP(B9,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>25.92</v>
       </c>
       <c r="F9" s="3" t="str">
-        <f>LOOKUP(C9,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C9,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>32.41</v>
       </c>
     </row>
@@ -1650,15 +1649,15 @@
         <v>37</v>
       </c>
       <c r="D10" s="3">
-        <f>LOOKUP(B10,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>381</v>
+        <f>LOOKUP(B10,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>387</v>
       </c>
       <c r="E10" s="3">
-        <f>LOOKUP(B10,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>56.87</v>
+        <f>LOOKUP(B10,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>56.9</v>
       </c>
       <c r="F10" s="3" t="str">
-        <f>LOOKUP(C10,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C10,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>59.13</v>
       </c>
     </row>
@@ -1673,15 +1672,15 @@
         <v>61</v>
       </c>
       <c r="D11" s="3">
-        <f>LOOKUP(B11,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>109</v>
+        <f>LOOKUP(B11,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>114</v>
       </c>
       <c r="E11" s="3">
-        <f>LOOKUP(B11,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>83.72</v>
+        <f>LOOKUP(B11,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>84.69</v>
       </c>
       <c r="F11" s="3" t="str">
-        <f>LOOKUP(C11,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C11,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>104.16</v>
       </c>
     </row>
@@ -1696,15 +1695,15 @@
         <v>55</v>
       </c>
       <c r="D12" s="3">
-        <f>LOOKUP(B12,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>129</v>
+        <f>LOOKUP(B12,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>133</v>
       </c>
       <c r="E12" s="3">
-        <f>LOOKUP(B12,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>138.02000000000001</v>
+        <f>LOOKUP(B12,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>138.41999999999999</v>
       </c>
       <c r="F12" s="3" t="str">
-        <f>LOOKUP(C12,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C12,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>151.63</v>
       </c>
     </row>
@@ -1719,15 +1718,15 @@
         <v>38</v>
       </c>
       <c r="D13" s="3">
-        <f>LOOKUP(B13,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>463</v>
+        <f>LOOKUP(B13,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>504</v>
       </c>
       <c r="E13" s="3">
-        <f>LOOKUP(B13,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>84.58</v>
+        <f>LOOKUP(B13,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>85.73</v>
       </c>
       <c r="F13" s="3" t="str">
-        <f>LOOKUP(C13,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C13,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>98.93</v>
       </c>
     </row>
@@ -1742,15 +1741,15 @@
         <v>56</v>
       </c>
       <c r="D14" s="3">
-        <f>LOOKUP(B14,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>935</v>
+        <f>LOOKUP(B14,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>989</v>
       </c>
       <c r="E14" s="3">
-        <f>LOOKUP(B14,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>38.119999999999997</v>
+        <f>LOOKUP(B14,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>38.26</v>
       </c>
       <c r="F14" s="3" t="str">
-        <f>LOOKUP(C14,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C14,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>39.45</v>
       </c>
     </row>
@@ -1765,15 +1764,15 @@
         <v>46</v>
       </c>
       <c r="D15" s="3">
-        <f>LOOKUP(B15,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>249</v>
+        <f>LOOKUP(B15,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>252</v>
       </c>
       <c r="E15" s="3">
-        <f>LOOKUP(B15,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>131.49</v>
+        <f>LOOKUP(B15,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>131.75</v>
       </c>
       <c r="F15" s="3" t="str">
-        <f>LOOKUP(C15,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C15,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>155.32</v>
       </c>
     </row>
@@ -1788,15 +1787,15 @@
         <v>59</v>
       </c>
       <c r="D16" s="3">
-        <f>LOOKUP(B16,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>380</v>
+        <f>LOOKUP(B16,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>385</v>
       </c>
       <c r="E16" s="3">
-        <f>LOOKUP(B16,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>49.28</v>
+        <f>LOOKUP(B16,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>49.51</v>
       </c>
       <c r="F16" s="3" t="str">
-        <f>LOOKUP(C16,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C16,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>68.88</v>
       </c>
     </row>
@@ -1811,15 +1810,15 @@
         <v>40</v>
       </c>
       <c r="D17" s="3">
-        <f>LOOKUP(B17,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>2075</v>
+        <f>LOOKUP(B17,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>2116</v>
       </c>
       <c r="E17" s="3">
-        <f>LOOKUP(B17,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>9.0399999999999991</v>
+        <f>LOOKUP(B17,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>9.07</v>
       </c>
       <c r="F17" s="3" t="str">
-        <f>LOOKUP(C17,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C17,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>10.44</v>
       </c>
     </row>
@@ -1834,15 +1833,15 @@
         <v>41</v>
       </c>
       <c r="D18" s="3">
-        <f>LOOKUP(B18,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>2129</v>
+        <f>LOOKUP(B18,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>2148</v>
       </c>
       <c r="E18" s="3">
-        <f>LOOKUP(B18,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>20.04</v>
+        <f>LOOKUP(B18,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>20.07</v>
       </c>
       <c r="F18" s="3" t="str">
-        <f>LOOKUP(C18,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C18,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>22.99</v>
       </c>
     </row>
@@ -1857,15 +1856,15 @@
         <v>45</v>
       </c>
       <c r="D19" s="3">
-        <f>LOOKUP(B19,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>1975</v>
+        <f>LOOKUP(B19,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>1988</v>
       </c>
       <c r="E19" s="3">
-        <f>LOOKUP(B19,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>27.34</v>
+        <f>LOOKUP(B19,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>27.37</v>
       </c>
       <c r="F19" s="3" t="str">
-        <f>LOOKUP(C19,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C19,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>30.82</v>
       </c>
     </row>
@@ -1880,15 +1879,15 @@
         <v>52</v>
       </c>
       <c r="D20" s="3">
-        <f>LOOKUP(B20,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>310</v>
+        <f>LOOKUP(B20,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>314</v>
       </c>
       <c r="E20" s="3">
-        <f>LOOKUP(B20,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>69.430000000000007</v>
+        <f>LOOKUP(B20,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>69.650000000000006</v>
       </c>
       <c r="F20" s="3" t="str">
-        <f>LOOKUP(C20,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C20,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>90.40</v>
       </c>
     </row>
@@ -1903,15 +1902,15 @@
         <v>57</v>
       </c>
       <c r="D21" s="3">
-        <f>LOOKUP(B21,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>218</v>
+        <f>LOOKUP(B21,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>220</v>
       </c>
       <c r="E21" s="3">
-        <f>LOOKUP(B21,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>174.02</v>
+        <f>LOOKUP(B21,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>174.53</v>
       </c>
       <c r="F21" s="3" t="str">
-        <f>LOOKUP(C21,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C21,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>234.28</v>
       </c>
     </row>
@@ -1926,15 +1925,15 @@
         <v>47</v>
       </c>
       <c r="D22" s="3">
-        <f>LOOKUP(B22,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>1553</v>
+        <f>LOOKUP(B22,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>1679</v>
       </c>
       <c r="E22" s="3">
-        <f>LOOKUP(B22,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>21.83</v>
+        <f>LOOKUP(B22,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>22</v>
       </c>
       <c r="F22" s="3" t="str">
-        <f>LOOKUP(C22,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C22,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>24.24</v>
       </c>
     </row>
@@ -1949,15 +1948,15 @@
         <v>50</v>
       </c>
       <c r="D23" s="3">
-        <f>LOOKUP(B23,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>379</v>
+        <f>LOOKUP(B23,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>383</v>
       </c>
       <c r="E23" s="3">
-        <f>LOOKUP(B23,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>85.71</v>
+        <f>LOOKUP(B23,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>85.75</v>
       </c>
       <c r="F23" s="3" t="str">
-        <f>LOOKUP(C23,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C23,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>92.88</v>
       </c>
     </row>
@@ -1972,15 +1971,15 @@
         <v>54</v>
       </c>
       <c r="D24" s="3">
-        <f>LOOKUP(B24,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>1625</v>
+        <f>LOOKUP(B24,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>1649</v>
       </c>
       <c r="E24" s="3">
-        <f>LOOKUP(B24,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>15.6</v>
+        <f>LOOKUP(B24,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>15.62</v>
       </c>
       <c r="F24" s="3" t="str">
-        <f>LOOKUP(C24,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C24,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>17.11</v>
       </c>
     </row>
@@ -1995,15 +1994,15 @@
         <v>48</v>
       </c>
       <c r="D25" s="3">
-        <f>LOOKUP(B25,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>115</v>
+        <f>LOOKUP(B25,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>129</v>
       </c>
       <c r="E25" s="3">
-        <f>LOOKUP(B25,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>258.17</v>
+        <f>LOOKUP(B25,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>261.92</v>
       </c>
       <c r="F25" s="3" t="str">
-        <f>LOOKUP(C25,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C25,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>291.44</v>
       </c>
     </row>
@@ -2018,15 +2017,15 @@
         <v>53</v>
       </c>
       <c r="D26" s="3">
-        <f>LOOKUP(B26,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>3306</v>
+        <f>LOOKUP(B26,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>3401</v>
       </c>
       <c r="E26" s="3">
-        <f>LOOKUP(B26,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>10.83</v>
+        <f>LOOKUP(B26,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>10.87</v>
       </c>
       <c r="F26" s="3" t="str">
-        <f>LOOKUP(C26,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C26,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>12.35</v>
       </c>
     </row>
@@ -2041,15 +2040,15 @@
         <v>33</v>
       </c>
       <c r="D27" s="3">
-        <f>LOOKUP(B27,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>652</v>
+        <f>LOOKUP(B27,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>671</v>
       </c>
       <c r="E27" s="3">
-        <f>LOOKUP(B27,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>61.96</v>
+        <f>LOOKUP(B27,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>62.6</v>
       </c>
       <c r="F27" s="3" t="str">
-        <f>LOOKUP(C27,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C27,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>85.85</v>
       </c>
     </row>
@@ -2064,15 +2063,15 @@
         <v>44</v>
       </c>
       <c r="D28" s="3">
-        <f>LOOKUP(B28,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>1623</v>
+        <f>LOOKUP(B28,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>1719</v>
       </c>
       <c r="E28" s="3">
-        <f>LOOKUP(B28,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>25.07</v>
+        <f>LOOKUP(B28,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>25.27</v>
       </c>
       <c r="F28" s="3" t="str">
-        <f>LOOKUP(C28,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C28,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>28.59</v>
       </c>
     </row>
@@ -2087,15 +2086,15 @@
         <v>36</v>
       </c>
       <c r="D29" s="3">
-        <f>LOOKUP(B29,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>41</v>
+        <f>LOOKUP(B29,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>43</v>
       </c>
       <c r="E29" s="3">
-        <f>LOOKUP(B29,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>863.71</v>
+        <f>LOOKUP(B29,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>868.84</v>
       </c>
       <c r="F29" s="3" t="str">
-        <f>LOOKUP(C29,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C29,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>967.96</v>
       </c>
     </row>
@@ -2110,15 +2109,15 @@
         <v>60</v>
       </c>
       <c r="D30" s="3">
-        <f>LOOKUP(B30,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>99</v>
+        <f>LOOKUP(B30,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>103</v>
       </c>
       <c r="E30" s="3">
-        <f>LOOKUP(B30,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>101.28</v>
+        <f>LOOKUP(B30,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>103.31</v>
       </c>
       <c r="F30" s="3" t="str">
-        <f>LOOKUP(C30,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C30,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>152.56</v>
       </c>
     </row>
@@ -2133,15 +2132,15 @@
         <v>49</v>
       </c>
       <c r="D31" s="3">
-        <f>LOOKUP(B31,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$C$14:$C$62)</f>
-        <v>502</v>
+        <f>LOOKUP(B31,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$C$14:$C$62)</f>
+        <v>508</v>
       </c>
       <c r="E31" s="3">
-        <f>LOOKUP(B31,'[2]Portfolio Summary Report'!$B$14:$B$62,'[2]Portfolio Summary Report'!$D$14:$D$62)</f>
-        <v>86.21</v>
+        <f>LOOKUP(B31,'[1]Portfolio Summary Report'!$B$14:$B$62,'[1]Portfolio Summary Report'!$D$14:$D$62)</f>
+        <v>86.35</v>
       </c>
       <c r="F31" s="3" t="str">
-        <f>LOOKUP(C31,[1]Watchlist!$B$2:$B$31,[1]Watchlist!$D$2:$D$31)</f>
+        <f>LOOKUP(C31,[2]Watchlist!$B$2:$B$31,[2]Watchlist!$D$2:$D$31)</f>
         <v>96.83</v>
       </c>
     </row>

--- a/ETF Summary Report.xlsx
+++ b/ETF Summary Report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Documents/Ventures/Hemrek Capital/Investment/ETF/Samhita/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manthan Patel\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE79F37-6A27-5F43-8AAF-24FD3E43DC94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{853FD7E1-CD51-4765-896B-C419FC1FB983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manthan" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Manthan!$B$1:$E$31</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="67">
   <si>
     <t>CPSE ETF</t>
   </si>
@@ -230,6 +229,12 @@
   </si>
   <si>
     <t>CPSEETF</t>
+  </si>
+  <si>
+    <t>Kotak Nifty Chemicals ETF</t>
+  </si>
+  <si>
+    <t>Groww BSE Power ETF</t>
   </si>
 </sst>
 </file>
@@ -608,14 +613,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8098D1ED-88A4-402D-8F82-419774D4C9BB}">
-  <dimension ref="A1:E31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="46.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="46.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
@@ -632,7 +637,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -643,13 +648,13 @@
         <v>34</v>
       </c>
       <c r="D2" s="3">
-        <v>2411</v>
+        <v>2541</v>
       </c>
       <c r="E2" s="4">
-        <v>22.846669431771051</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+        <v>23.173636363636383</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -663,10 +668,10 @@
         <v>890</v>
       </c>
       <c r="E3" s="4">
-        <v>52.456438202247206</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>52.444078651685402</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -677,13 +682,13 @@
         <v>39</v>
       </c>
       <c r="D4" s="3">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="E4" s="4">
-        <v>81.518695652173832</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+        <v>81.573901960784426</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -694,13 +699,13 @@
         <v>42</v>
       </c>
       <c r="D5" s="3">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="E5" s="4">
-        <v>113.11283333333333</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+        <v>113.30409836065574</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -711,13 +716,13 @@
         <v>64</v>
       </c>
       <c r="D6" s="3">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="E6" s="4">
-        <v>83.990083102493116</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+        <v>84.544528795811544</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -728,13 +733,13 @@
         <v>58</v>
       </c>
       <c r="D7" s="3">
-        <v>1122</v>
+        <v>1176</v>
       </c>
       <c r="E7" s="4">
-        <v>21.922869875222784</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+        <v>21.993214285714302</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -745,13 +750,13 @@
         <v>51</v>
       </c>
       <c r="D8" s="3">
-        <v>1554</v>
+        <v>1580</v>
       </c>
       <c r="E8" s="4">
-        <v>27.828384813384851</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+        <v>27.878696202531625</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -762,13 +767,13 @@
         <v>43</v>
       </c>
       <c r="D9" s="3">
-        <v>1737</v>
+        <v>1845</v>
       </c>
       <c r="E9" s="4">
-        <v>26.545607369027074</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+        <v>26.918921409214111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -779,13 +784,13 @@
         <v>37</v>
       </c>
       <c r="D10" s="3">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="E10" s="4">
-        <v>57.149624413145517</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+        <v>57.091070615034191</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -796,13 +801,13 @@
         <v>61</v>
       </c>
       <c r="D11" s="3">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="E11" s="4">
-        <v>85.992833333333323</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+        <v>91.327724137931057</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -813,13 +818,13 @@
         <v>55</v>
       </c>
       <c r="D12" s="3">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="E12" s="4">
-        <v>139.34380281690136</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+        <v>140.96814814814812</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -830,13 +835,13 @@
         <v>38</v>
       </c>
       <c r="D13" s="3">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="E13" s="4">
-        <v>86.604182156133916</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+        <v>86.649372693726974</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -847,13 +852,13 @@
         <v>56</v>
       </c>
       <c r="D14" s="3">
-        <v>1175</v>
+        <v>1186</v>
       </c>
       <c r="E14" s="4">
-        <v>38.722910638297861</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+        <v>38.765480607082615</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -864,13 +869,13 @@
         <v>46</v>
       </c>
       <c r="D15" s="3">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E15" s="4">
-        <v>134.05569892473122</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+        <v>134.5244912280703</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -881,13 +886,13 @@
         <v>59</v>
       </c>
       <c r="D16" s="3">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="E16" s="4">
-        <v>49.622067183462534</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+        <v>50.940097323600966</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -898,13 +903,13 @@
         <v>40</v>
       </c>
       <c r="D17" s="3">
-        <v>2288</v>
+        <v>2331</v>
       </c>
       <c r="E17" s="4">
-        <v>9.2176223776223836</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+        <v>9.232608322608332</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -915,13 +920,13 @@
         <v>41</v>
       </c>
       <c r="D18" s="3">
-        <v>2403</v>
+        <v>2424</v>
       </c>
       <c r="E18" s="4">
-        <v>20.409729504785666</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+        <v>20.423122937293716</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -932,13 +937,13 @@
         <v>45</v>
       </c>
       <c r="D19" s="3">
-        <v>2009</v>
+        <v>2024</v>
       </c>
       <c r="E19" s="4">
-        <v>27.408272772523638</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+        <v>27.424313241106717</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -949,13 +954,13 @@
         <v>52</v>
       </c>
       <c r="D20" s="3">
-        <v>325</v>
+        <v>381</v>
       </c>
       <c r="E20" s="4">
-        <v>70.252769230769303</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+        <v>72.839658792650923</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -966,13 +971,13 @@
         <v>57</v>
       </c>
       <c r="D21" s="3">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="E21" s="4">
-        <v>175.62031249999993</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+        <v>180.53229508196722</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -983,13 +988,13 @@
         <v>47</v>
       </c>
       <c r="D22" s="3">
-        <v>1828</v>
+        <v>1852</v>
       </c>
       <c r="E22" s="4">
-        <v>22.218971553610551</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+        <v>22.228509719222501</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1000,13 +1005,13 @@
         <v>50</v>
       </c>
       <c r="D23" s="3">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="E23" s="4">
-        <v>85.850203045685305</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+        <v>85.925062344139604</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1017,13 +1022,13 @@
         <v>54</v>
       </c>
       <c r="D24" s="3">
-        <v>1707</v>
+        <v>1736</v>
       </c>
       <c r="E24" s="4">
-        <v>15.656045694200349</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+        <v>15.667396313364058</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1034,13 +1039,13 @@
         <v>48</v>
       </c>
       <c r="D25" s="3">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E25" s="4">
-        <v>263.9876086956516</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+        <v>264.24604316546771</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1051,13 +1056,13 @@
         <v>53</v>
       </c>
       <c r="D26" s="3">
-        <v>3532</v>
+        <v>3573</v>
       </c>
       <c r="E26" s="4">
-        <v>10.904852774631928</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+        <v>10.913677581863974</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1068,13 +1073,13 @@
         <v>33</v>
       </c>
       <c r="D27" s="3">
-        <v>679</v>
+        <v>728</v>
       </c>
       <c r="E27" s="4">
-        <v>62.875316642120801</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+        <v>64.581428571428603</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1085,13 +1090,13 @@
         <v>44</v>
       </c>
       <c r="D28" s="3">
-        <v>1819</v>
+        <v>1941</v>
       </c>
       <c r="E28" s="4">
-        <v>25.498119846069262</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+        <v>25.710607934054615</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1105,10 +1110,10 @@
         <v>48</v>
       </c>
       <c r="E29" s="4">
-        <v>880.09104166666657</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+        <v>880.12874999999985</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -1119,13 +1124,13 @@
         <v>60</v>
       </c>
       <c r="D30" s="3">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E30" s="4">
-        <v>106.58981481481479</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+        <v>108.94163636363638</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -1136,10 +1141,44 @@
         <v>49</v>
       </c>
       <c r="D31" s="3">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="E31" s="4">
-        <v>86.546395348837208</v>
+        <v>86.632403846153835</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D32" s="3">
+        <v>46</v>
+      </c>
+      <c r="E32" s="4">
+        <v>28.97</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" s="3">
+        <v>150</v>
+      </c>
+      <c r="E33" s="4">
+        <v>9.6999999999999993</v>
       </c>
     </row>
   </sheetData>

--- a/ETF Summary Report.xlsx
+++ b/ETF Summary Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manthan Patel\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{853FD7E1-CD51-4765-896B-C419FC1FB983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F8280FB-7DA0-400B-ABC1-788365329D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>CPSE ETF</t>
   </si>
@@ -235,6 +235,12 @@
   </si>
   <si>
     <t>Groww BSE Power ETF</t>
+  </si>
+  <si>
+    <t>GROWWPOWER</t>
+  </si>
+  <si>
+    <t>CHEMICAL</t>
   </si>
 </sst>
 </file>
@@ -1155,7 +1161,7 @@
         <v>65</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="D32" s="3">
         <v>46</v>
@@ -1172,7 +1178,7 @@
         <v>66</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D33" s="3">
         <v>150</v>

--- a/ETF Summary Report.xlsx
+++ b/ETF Summary Report.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078A5B8F-3DC4-AB4F-9D42-F7D95E10B665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B8AC532-EAD6-CD40-A132-40A06B8F8140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manthan" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -24,6 +24,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>SR. NO.</t>
   </si>
@@ -55,12 +56,6 @@
     <t>AUTOIETF</t>
   </si>
   <si>
-    <t>ICICI Prudential Nifty Bank ETF</t>
-  </si>
-  <si>
-    <t>BANKIETF</t>
-  </si>
-  <si>
     <t>ICICI Prudential Nifty Commodities ETF</t>
   </si>
   <si>
@@ -205,12 +200,6 @@
     <t>PVTBANIETF</t>
   </si>
   <si>
-    <t>ICICI Prudential BSE Sensex ETF</t>
-  </si>
-  <si>
-    <t>SENSEXIETF</t>
-  </si>
-  <si>
     <t>Tata Nifty India Digital ETF</t>
   </si>
   <si>
@@ -227,18 +216,6 @@
   </si>
   <si>
     <t>Kotak Nifty Chemicals ETF</t>
-  </si>
-  <si>
-    <t>GOLDIETF</t>
-  </si>
-  <si>
-    <t>SILVERIETF</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Gold ETF</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Silver ETF</t>
   </si>
 </sst>
 </file>
@@ -299,7 +276,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -307,8 +284,6 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1439,7 +1414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1" customWidth="1"/>
@@ -1477,10 +1452,10 @@
         <v>6</v>
       </c>
       <c r="D2" s="5">
-        <v>2593</v>
+        <v>143</v>
       </c>
       <c r="E2" s="6">
-        <v>23.28294253760124</v>
+        <v>29.05</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1494,10 +1469,10 @@
         <v>8</v>
       </c>
       <c r="D3" s="5">
-        <v>890</v>
+        <v>123</v>
       </c>
       <c r="E3" s="6">
-        <v>52.444078651685402</v>
+        <v>101.24</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1511,10 +1486,10 @@
         <v>10</v>
       </c>
       <c r="D4" s="5">
-        <v>555</v>
+        <v>17</v>
       </c>
       <c r="E4" s="6">
-        <v>82.89648648648668</v>
+        <v>119.9</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1528,10 +1503,10 @@
         <v>12</v>
       </c>
       <c r="D5" s="5">
-        <v>371</v>
+        <v>205</v>
       </c>
       <c r="E5" s="6">
-        <v>113.39371967654985</v>
+        <v>102.99</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1545,10 +1520,10 @@
         <v>14</v>
       </c>
       <c r="D6" s="5">
-        <v>458</v>
+        <v>85</v>
       </c>
       <c r="E6" s="6">
-        <v>86.733187772925746</v>
+        <v>24.75</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1562,10 +1537,10 @@
         <v>16</v>
       </c>
       <c r="D7" s="5">
-        <v>1206</v>
+        <v>112</v>
       </c>
       <c r="E7" s="6">
-        <v>22.017379767827546</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1579,10 +1554,10 @@
         <v>18</v>
       </c>
       <c r="D8" s="5">
-        <v>1620</v>
+        <v>140</v>
       </c>
       <c r="E8" s="6">
-        <v>28.002592592592563</v>
+        <v>32.32</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1596,10 +1571,10 @@
         <v>20</v>
       </c>
       <c r="D9" s="5">
-        <v>1897</v>
+        <v>36</v>
       </c>
       <c r="E9" s="6">
-        <v>27.036199261992643</v>
+        <v>54.97</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1613,15 +1588,15 @@
         <v>22</v>
       </c>
       <c r="D10" s="5">
-        <v>451</v>
+        <v>16</v>
       </c>
       <c r="E10" s="6">
-        <v>57.003813747228385</v>
+        <v>154.41</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>23</v>
@@ -1630,15 +1605,15 @@
         <v>24</v>
       </c>
       <c r="D11" s="5">
-        <v>167</v>
+        <v>21</v>
       </c>
       <c r="E11" s="6">
-        <v>141.05047904191622</v>
+        <v>98.05</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>25</v>
@@ -1647,15 +1622,15 @@
         <v>26</v>
       </c>
       <c r="D12" s="5">
-        <v>549</v>
+        <v>118</v>
       </c>
       <c r="E12" s="6">
-        <v>86.744335154826985</v>
+        <v>33.79</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>27</v>
@@ -1664,15 +1639,15 @@
         <v>28</v>
       </c>
       <c r="D13" s="5">
-        <v>1228</v>
+        <v>130</v>
       </c>
       <c r="E13" s="6">
-        <v>38.863322475570058</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>29</v>
@@ -1681,15 +1656,15 @@
         <v>30</v>
       </c>
       <c r="D14" s="5">
-        <v>288</v>
+        <v>21</v>
       </c>
       <c r="E14" s="6">
-        <v>134.79833333333349</v>
+        <v>70.44</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>31</v>
@@ -1698,15 +1673,15 @@
         <v>32</v>
       </c>
       <c r="D15" s="5">
-        <v>483</v>
+        <v>848</v>
       </c>
       <c r="E15" s="6">
-        <v>53.984430641821938</v>
+        <v>12.31</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>33</v>
@@ -1715,15 +1690,15 @@
         <v>34</v>
       </c>
       <c r="D16" s="5">
-        <v>2648</v>
+        <v>90</v>
       </c>
       <c r="E16" s="6">
-        <v>9.5092296072507558</v>
+        <v>22.59</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>35</v>
@@ -1732,15 +1707,15 @@
         <v>36</v>
       </c>
       <c r="D17" s="5">
-        <v>2456</v>
+        <v>135</v>
       </c>
       <c r="E17" s="6">
-        <v>20.422968241042369</v>
+        <v>32.71</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>37</v>
@@ -1749,15 +1724,15 @@
         <v>38</v>
       </c>
       <c r="D18" s="5">
-        <v>2075</v>
+        <v>224</v>
       </c>
       <c r="E18" s="6">
-        <v>27.522674698795182</v>
+        <v>89.31</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>39</v>
@@ -1766,15 +1741,15 @@
         <v>40</v>
       </c>
       <c r="D19" s="5">
-        <v>430</v>
+        <v>34</v>
       </c>
       <c r="E19" s="6">
-        <v>74.685000000000045</v>
+        <v>224.5</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>41</v>
@@ -1783,15 +1758,15 @@
         <v>42</v>
       </c>
       <c r="D20" s="5">
-        <v>256</v>
+        <v>85</v>
       </c>
       <c r="E20" s="6">
-        <v>182.79781249999996</v>
+        <v>23.69</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>43</v>
@@ -1800,15 +1775,15 @@
         <v>44</v>
       </c>
       <c r="D21" s="5">
-        <v>1882</v>
+        <v>25</v>
       </c>
       <c r="E21" s="6">
-        <v>22.229744952178535</v>
+        <v>78.22</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>45</v>
@@ -1817,15 +1792,15 @@
         <v>46</v>
       </c>
       <c r="D22" s="5">
-        <v>402</v>
+        <v>127</v>
       </c>
       <c r="E22" s="6">
-        <v>85.895522388059703</v>
+        <v>16.02</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>47</v>
@@ -1834,15 +1809,15 @@
         <v>48</v>
       </c>
       <c r="D23" s="5">
-        <v>1783</v>
+        <v>7</v>
       </c>
       <c r="E23" s="6">
-        <v>15.657947279865384</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>49</v>
@@ -1851,15 +1826,15 @@
         <v>50</v>
       </c>
       <c r="D24" s="5">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="E24" s="6">
-        <v>264.56760563380266</v>
+        <v>12.39</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>51</v>
@@ -1868,15 +1843,15 @@
         <v>52</v>
       </c>
       <c r="D25" s="5">
-        <v>3635</v>
+        <v>220</v>
       </c>
       <c r="E25" s="6">
-        <v>10.941584594222835</v>
+        <v>99.46</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>53</v>
@@ -1885,15 +1860,15 @@
         <v>54</v>
       </c>
       <c r="D26" s="5">
-        <v>810</v>
+        <v>403</v>
       </c>
       <c r="E26" s="6">
-        <v>67.108518518518622</v>
+        <v>28.86</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>55</v>
@@ -1902,112 +1877,44 @@
         <v>56</v>
       </c>
       <c r="D27" s="5">
-        <v>2091</v>
+        <v>21</v>
       </c>
       <c r="E27" s="6">
-        <v>25.924404591104746</v>
+        <v>83.88</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>58</v>
-      </c>
       <c r="D28" s="5">
-        <v>48</v>
+        <v>209</v>
       </c>
       <c r="E28" s="6">
-        <v>880.12874999999985</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D29" s="5">
-        <v>527</v>
+        <v>72</v>
       </c>
       <c r="E29" s="6">
-        <v>86.722201138519935</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="3">
-        <v>31</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D30" s="5">
-        <v>227</v>
-      </c>
-      <c r="E30" s="6">
-        <v>9.7084140969162966</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="3">
-        <v>32</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D31" s="5">
-        <v>72</v>
-      </c>
-      <c r="E31" s="6">
-        <v>28.560000000000002</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="3">
-        <v>33</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D32" s="5">
-        <v>174</v>
-      </c>
-      <c r="E32" s="6">
-        <v>97.47</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="3">
-        <v>34</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D33" s="5">
-        <v>117</v>
-      </c>
-      <c r="E33" s="6">
-        <v>118.38</v>
+        <v>28.4</v>
       </c>
     </row>
   </sheetData>

--- a/ETF Summary Report.xlsx
+++ b/ETF Summary Report.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B8AC532-EAD6-CD40-A132-40A06B8F8140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078A5B8F-3DC4-AB4F-9D42-F7D95E10B665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manthan" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -24,7 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>SR. NO.</t>
   </si>
@@ -56,6 +55,12 @@
     <t>AUTOIETF</t>
   </si>
   <si>
+    <t>ICICI Prudential Nifty Bank ETF</t>
+  </si>
+  <si>
+    <t>BANKIETF</t>
+  </si>
+  <si>
     <t>ICICI Prudential Nifty Commodities ETF</t>
   </si>
   <si>
@@ -200,6 +205,12 @@
     <t>PVTBANIETF</t>
   </si>
   <si>
+    <t>ICICI Prudential BSE Sensex ETF</t>
+  </si>
+  <si>
+    <t>SENSEXIETF</t>
+  </si>
+  <si>
     <t>Tata Nifty India Digital ETF</t>
   </si>
   <si>
@@ -216,6 +227,18 @@
   </si>
   <si>
     <t>Kotak Nifty Chemicals ETF</t>
+  </si>
+  <si>
+    <t>GOLDIETF</t>
+  </si>
+  <si>
+    <t>SILVERIETF</t>
+  </si>
+  <si>
+    <t>ICICI Prudential Gold ETF</t>
+  </si>
+  <si>
+    <t>ICICI Prudential Silver ETF</t>
   </si>
 </sst>
 </file>
@@ -276,7 +299,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -284,6 +307,8 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1414,7 +1439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1" customWidth="1"/>
@@ -1452,10 +1477,10 @@
         <v>6</v>
       </c>
       <c r="D2" s="5">
-        <v>143</v>
+        <v>2593</v>
       </c>
       <c r="E2" s="6">
-        <v>29.05</v>
+        <v>23.28294253760124</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1469,10 +1494,10 @@
         <v>8</v>
       </c>
       <c r="D3" s="5">
-        <v>123</v>
+        <v>890</v>
       </c>
       <c r="E3" s="6">
-        <v>101.24</v>
+        <v>52.444078651685402</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1486,10 +1511,10 @@
         <v>10</v>
       </c>
       <c r="D4" s="5">
-        <v>17</v>
+        <v>555</v>
       </c>
       <c r="E4" s="6">
-        <v>119.9</v>
+        <v>82.89648648648668</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1503,10 +1528,10 @@
         <v>12</v>
       </c>
       <c r="D5" s="5">
-        <v>205</v>
+        <v>371</v>
       </c>
       <c r="E5" s="6">
-        <v>102.99</v>
+        <v>113.39371967654985</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1520,10 +1545,10 @@
         <v>14</v>
       </c>
       <c r="D6" s="5">
-        <v>85</v>
+        <v>458</v>
       </c>
       <c r="E6" s="6">
-        <v>24.75</v>
+        <v>86.733187772925746</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1537,10 +1562,10 @@
         <v>16</v>
       </c>
       <c r="D7" s="5">
-        <v>112</v>
+        <v>1206</v>
       </c>
       <c r="E7" s="6">
-        <v>31</v>
+        <v>22.017379767827546</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1554,10 +1579,10 @@
         <v>18</v>
       </c>
       <c r="D8" s="5">
-        <v>140</v>
+        <v>1620</v>
       </c>
       <c r="E8" s="6">
-        <v>32.32</v>
+        <v>28.002592592592563</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1571,10 +1596,10 @@
         <v>20</v>
       </c>
       <c r="D9" s="5">
-        <v>36</v>
+        <v>1897</v>
       </c>
       <c r="E9" s="6">
-        <v>54.97</v>
+        <v>27.036199261992643</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1588,15 +1613,15 @@
         <v>22</v>
       </c>
       <c r="D10" s="5">
-        <v>16</v>
+        <v>451</v>
       </c>
       <c r="E10" s="6">
-        <v>154.41</v>
+        <v>57.003813747228385</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>23</v>
@@ -1605,15 +1630,15 @@
         <v>24</v>
       </c>
       <c r="D11" s="5">
-        <v>21</v>
+        <v>167</v>
       </c>
       <c r="E11" s="6">
-        <v>98.05</v>
+        <v>141.05047904191622</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>25</v>
@@ -1622,15 +1647,15 @@
         <v>26</v>
       </c>
       <c r="D12" s="5">
-        <v>118</v>
+        <v>549</v>
       </c>
       <c r="E12" s="6">
-        <v>33.79</v>
+        <v>86.744335154826985</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>27</v>
@@ -1639,15 +1664,15 @@
         <v>28</v>
       </c>
       <c r="D13" s="5">
-        <v>130</v>
+        <v>1228</v>
       </c>
       <c r="E13" s="6">
-        <v>160</v>
+        <v>38.863322475570058</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>29</v>
@@ -1656,15 +1681,15 @@
         <v>30</v>
       </c>
       <c r="D14" s="5">
-        <v>21</v>
+        <v>288</v>
       </c>
       <c r="E14" s="6">
-        <v>70.44</v>
+        <v>134.79833333333349</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>31</v>
@@ -1673,15 +1698,15 @@
         <v>32</v>
       </c>
       <c r="D15" s="5">
-        <v>848</v>
+        <v>483</v>
       </c>
       <c r="E15" s="6">
-        <v>12.31</v>
+        <v>53.984430641821938</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>33</v>
@@ -1690,15 +1715,15 @@
         <v>34</v>
       </c>
       <c r="D16" s="5">
-        <v>90</v>
+        <v>2648</v>
       </c>
       <c r="E16" s="6">
-        <v>22.59</v>
+        <v>9.5092296072507558</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>35</v>
@@ -1707,15 +1732,15 @@
         <v>36</v>
       </c>
       <c r="D17" s="5">
-        <v>135</v>
+        <v>2456</v>
       </c>
       <c r="E17" s="6">
-        <v>32.71</v>
+        <v>20.422968241042369</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>37</v>
@@ -1724,15 +1749,15 @@
         <v>38</v>
       </c>
       <c r="D18" s="5">
-        <v>224</v>
+        <v>2075</v>
       </c>
       <c r="E18" s="6">
-        <v>89.31</v>
+        <v>27.522674698795182</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>39</v>
@@ -1741,15 +1766,15 @@
         <v>40</v>
       </c>
       <c r="D19" s="5">
-        <v>34</v>
+        <v>430</v>
       </c>
       <c r="E19" s="6">
-        <v>224.5</v>
+        <v>74.685000000000045</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>41</v>
@@ -1758,15 +1783,15 @@
         <v>42</v>
       </c>
       <c r="D20" s="5">
-        <v>85</v>
+        <v>256</v>
       </c>
       <c r="E20" s="6">
-        <v>23.69</v>
+        <v>182.79781249999996</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>43</v>
@@ -1775,15 +1800,15 @@
         <v>44</v>
       </c>
       <c r="D21" s="5">
-        <v>25</v>
+        <v>1882</v>
       </c>
       <c r="E21" s="6">
-        <v>78.22</v>
+        <v>22.229744952178535</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>45</v>
@@ -1792,15 +1817,15 @@
         <v>46</v>
       </c>
       <c r="D22" s="5">
-        <v>127</v>
+        <v>402</v>
       </c>
       <c r="E22" s="6">
-        <v>16.02</v>
+        <v>85.895522388059703</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>47</v>
@@ -1809,15 +1834,15 @@
         <v>48</v>
       </c>
       <c r="D23" s="5">
-        <v>7</v>
+        <v>1783</v>
       </c>
       <c r="E23" s="6">
-        <v>284</v>
+        <v>15.657947279865384</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>49</v>
@@ -1826,15 +1851,15 @@
         <v>50</v>
       </c>
       <c r="D24" s="5">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="E24" s="6">
-        <v>12.39</v>
+        <v>264.56760563380266</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>51</v>
@@ -1843,15 +1868,15 @@
         <v>52</v>
       </c>
       <c r="D25" s="5">
-        <v>220</v>
+        <v>3635</v>
       </c>
       <c r="E25" s="6">
-        <v>99.46</v>
+        <v>10.941584594222835</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>53</v>
@@ -1860,15 +1885,15 @@
         <v>54</v>
       </c>
       <c r="D26" s="5">
-        <v>403</v>
+        <v>810</v>
       </c>
       <c r="E26" s="6">
-        <v>28.86</v>
+        <v>67.108518518518622</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>55</v>
@@ -1877,44 +1902,112 @@
         <v>56</v>
       </c>
       <c r="D27" s="5">
-        <v>21</v>
+        <v>2091</v>
       </c>
       <c r="E27" s="6">
-        <v>83.88</v>
+        <v>25.924404591104746</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D28" s="5">
-        <v>209</v>
+        <v>48</v>
       </c>
       <c r="E28" s="6">
-        <v>10.6</v>
+        <v>880.12874999999985</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>58</v>
-      </c>
       <c r="D29" s="5">
+        <v>527</v>
+      </c>
+      <c r="E29" s="6">
+        <v>86.722201138519935</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="3">
+        <v>31</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D30" s="5">
+        <v>227</v>
+      </c>
+      <c r="E30" s="6">
+        <v>9.7084140969162966</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="3">
+        <v>32</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" s="5">
         <v>72</v>
       </c>
-      <c r="E29" s="6">
-        <v>28.4</v>
+      <c r="E31" s="6">
+        <v>28.560000000000002</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="3">
+        <v>33</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D32" s="5">
+        <v>174</v>
+      </c>
+      <c r="E32" s="6">
+        <v>97.47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="3">
+        <v>34</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D33" s="5">
+        <v>117</v>
+      </c>
+      <c r="E33" s="6">
+        <v>118.38</v>
       </c>
     </row>
   </sheetData>

--- a/ETF Summary Report.xlsx
+++ b/ETF Summary Report.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078A5B8F-3DC4-AB4F-9D42-F7D95E10B665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F37A6FAF-34A6-E54B-8021-B106CA181F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manthan" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -24,6 +24,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -299,14 +300,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -1477,10 +1477,10 @@
         <v>6</v>
       </c>
       <c r="D2" s="5">
-        <v>2593</v>
-      </c>
-      <c r="E2" s="6">
-        <v>23.28294253760124</v>
+        <v>2723</v>
+      </c>
+      <c r="E2" s="5">
+        <v>23.5</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1496,8 +1496,8 @@
       <c r="D3" s="5">
         <v>890</v>
       </c>
-      <c r="E3" s="6">
-        <v>52.444078651685402</v>
+      <c r="E3" s="5">
+        <v>52.48</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1511,10 +1511,10 @@
         <v>10</v>
       </c>
       <c r="D4" s="5">
-        <v>555</v>
-      </c>
-      <c r="E4" s="6">
-        <v>82.89648648648668</v>
+        <v>590</v>
+      </c>
+      <c r="E4" s="5">
+        <v>83.84</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1528,10 +1528,10 @@
         <v>12</v>
       </c>
       <c r="D5" s="5">
-        <v>371</v>
-      </c>
-      <c r="E5" s="6">
-        <v>113.39371967654985</v>
+        <v>385</v>
+      </c>
+      <c r="E5" s="5">
+        <v>113.42</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1545,10 +1545,10 @@
         <v>14</v>
       </c>
       <c r="D6" s="5">
-        <v>458</v>
-      </c>
-      <c r="E6" s="6">
-        <v>86.733187772925746</v>
+        <v>523</v>
+      </c>
+      <c r="E6" s="5">
+        <v>88.42</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1562,10 +1562,10 @@
         <v>16</v>
       </c>
       <c r="D7" s="5">
-        <v>1206</v>
-      </c>
-      <c r="E7" s="6">
-        <v>22.017379767827546</v>
+        <v>1309</v>
+      </c>
+      <c r="E7" s="5">
+        <v>22.19</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1579,10 +1579,10 @@
         <v>18</v>
       </c>
       <c r="D8" s="5">
-        <v>1620</v>
-      </c>
-      <c r="E8" s="6">
-        <v>28.002592592592563</v>
+        <v>1703</v>
+      </c>
+      <c r="E8" s="5">
+        <v>28.08</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1596,10 +1596,10 @@
         <v>20</v>
       </c>
       <c r="D9" s="5">
-        <v>1897</v>
-      </c>
-      <c r="E9" s="6">
-        <v>27.036199261992643</v>
+        <v>1984</v>
+      </c>
+      <c r="E9" s="5">
+        <v>27.22</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1613,10 +1613,10 @@
         <v>22</v>
       </c>
       <c r="D10" s="5">
-        <v>451</v>
-      </c>
-      <c r="E10" s="6">
-        <v>57.003813747228385</v>
+        <v>478</v>
+      </c>
+      <c r="E10" s="5">
+        <v>56.85</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1630,10 +1630,10 @@
         <v>24</v>
       </c>
       <c r="D11" s="5">
-        <v>167</v>
-      </c>
-      <c r="E11" s="6">
-        <v>141.05047904191622</v>
+        <v>203</v>
+      </c>
+      <c r="E11" s="5">
+        <v>142.65</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1647,10 +1647,10 @@
         <v>26</v>
       </c>
       <c r="D12" s="5">
-        <v>549</v>
-      </c>
-      <c r="E12" s="6">
-        <v>86.744335154826985</v>
+        <v>574</v>
+      </c>
+      <c r="E12" s="5">
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1664,10 +1664,10 @@
         <v>28</v>
       </c>
       <c r="D13" s="5">
-        <v>1228</v>
-      </c>
-      <c r="E13" s="6">
-        <v>38.863322475570058</v>
+        <v>1281</v>
+      </c>
+      <c r="E13" s="5">
+        <v>38.75</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1681,10 +1681,10 @@
         <v>30</v>
       </c>
       <c r="D14" s="5">
-        <v>288</v>
-      </c>
-      <c r="E14" s="6">
-        <v>134.79833333333349</v>
+        <v>310</v>
+      </c>
+      <c r="E14" s="5">
+        <v>136.30000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1698,10 +1698,10 @@
         <v>32</v>
       </c>
       <c r="D15" s="5">
-        <v>483</v>
-      </c>
-      <c r="E15" s="6">
-        <v>53.984430641821938</v>
+        <v>516</v>
+      </c>
+      <c r="E15" s="5">
+        <v>55.03</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1715,10 +1715,10 @@
         <v>34</v>
       </c>
       <c r="D16" s="5">
-        <v>2648</v>
-      </c>
-      <c r="E16" s="6">
-        <v>9.5092296072507558</v>
+        <v>3022</v>
+      </c>
+      <c r="E16" s="5">
+        <v>9.82</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1732,10 +1732,10 @@
         <v>36</v>
       </c>
       <c r="D17" s="5">
-        <v>2456</v>
-      </c>
-      <c r="E17" s="6">
-        <v>20.422968241042369</v>
+        <v>2539</v>
+      </c>
+      <c r="E17" s="5">
+        <v>20.48</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1749,10 +1749,10 @@
         <v>38</v>
       </c>
       <c r="D18" s="5">
-        <v>2075</v>
-      </c>
-      <c r="E18" s="6">
-        <v>27.522674698795182</v>
+        <v>2261</v>
+      </c>
+      <c r="E18" s="5">
+        <v>27.89</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1766,10 +1766,10 @@
         <v>40</v>
       </c>
       <c r="D19" s="5">
-        <v>430</v>
-      </c>
-      <c r="E19" s="6">
-        <v>74.685000000000045</v>
+        <v>505</v>
+      </c>
+      <c r="E19" s="5">
+        <v>76.77</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1783,10 +1783,10 @@
         <v>42</v>
       </c>
       <c r="D20" s="5">
-        <v>256</v>
-      </c>
-      <c r="E20" s="6">
-        <v>182.79781249999996</v>
+        <v>237</v>
+      </c>
+      <c r="E20" s="5">
+        <v>9.1199999999999992</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1800,10 +1800,10 @@
         <v>44</v>
       </c>
       <c r="D21" s="5">
-        <v>1882</v>
-      </c>
-      <c r="E21" s="6">
-        <v>22.229744952178535</v>
+        <v>1938</v>
+      </c>
+      <c r="E21" s="5">
+        <v>22.26</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1817,10 +1817,10 @@
         <v>46</v>
       </c>
       <c r="D22" s="5">
-        <v>402</v>
-      </c>
-      <c r="E22" s="6">
-        <v>85.895522388059703</v>
+        <v>409</v>
+      </c>
+      <c r="E22" s="5">
+        <v>85.68</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1834,10 +1834,10 @@
         <v>48</v>
       </c>
       <c r="D23" s="5">
-        <v>1783</v>
-      </c>
-      <c r="E23" s="6">
-        <v>15.657947279865384</v>
+        <v>1881</v>
+      </c>
+      <c r="E23" s="5">
+        <v>15.67</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1851,10 +1851,10 @@
         <v>50</v>
       </c>
       <c r="D24" s="5">
-        <v>142</v>
-      </c>
-      <c r="E24" s="6">
-        <v>264.56760563380266</v>
+        <v>148</v>
+      </c>
+      <c r="E24" s="5">
+        <v>265.08999999999997</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1868,10 +1868,10 @@
         <v>52</v>
       </c>
       <c r="D25" s="5">
-        <v>3635</v>
-      </c>
-      <c r="E25" s="6">
-        <v>10.941584594222835</v>
+        <v>3812</v>
+      </c>
+      <c r="E25" s="5">
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1885,10 +1885,10 @@
         <v>54</v>
       </c>
       <c r="D26" s="5">
-        <v>810</v>
-      </c>
-      <c r="E26" s="6">
-        <v>67.108518518518622</v>
+        <v>868</v>
+      </c>
+      <c r="E26" s="5">
+        <v>68.86</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1902,10 +1902,10 @@
         <v>56</v>
       </c>
       <c r="D27" s="5">
-        <v>2091</v>
-      </c>
-      <c r="E27" s="6">
-        <v>25.924404591104746</v>
+        <v>2230</v>
+      </c>
+      <c r="E27" s="5">
+        <v>26.1</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1921,8 +1921,8 @@
       <c r="D28" s="5">
         <v>48</v>
       </c>
-      <c r="E28" s="6">
-        <v>880.12874999999985</v>
+      <c r="E28" s="5">
+        <v>880.09</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1936,10 +1936,10 @@
         <v>60</v>
       </c>
       <c r="D29" s="5">
-        <v>527</v>
-      </c>
-      <c r="E29" s="6">
-        <v>86.722201138519935</v>
+        <v>543</v>
+      </c>
+      <c r="E29" s="5">
+        <v>86.59</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1953,10 +1953,10 @@
         <v>61</v>
       </c>
       <c r="D30" s="5">
-        <v>227</v>
-      </c>
-      <c r="E30" s="6">
-        <v>9.7084140969162966</v>
+        <v>483</v>
+      </c>
+      <c r="E30" s="5">
+        <v>10.039999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1970,44 +1970,44 @@
         <v>62</v>
       </c>
       <c r="D31" s="5">
-        <v>72</v>
-      </c>
-      <c r="E31" s="6">
-        <v>28.560000000000002</v>
+        <v>181</v>
+      </c>
+      <c r="E31" s="5">
+        <v>27.94</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>33</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="6" t="s">
         <v>65</v>
       </c>
       <c r="D32" s="5">
-        <v>174</v>
-      </c>
-      <c r="E32" s="6">
-        <v>97.47</v>
+        <v>192</v>
+      </c>
+      <c r="E32" s="5">
+        <v>100.91</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>34</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="6" t="s">
         <v>66</v>
       </c>
       <c r="D33" s="5">
-        <v>117</v>
-      </c>
-      <c r="E33" s="6">
-        <v>118.38</v>
+        <v>130</v>
+      </c>
+      <c r="E33" s="5">
+        <v>132.55000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/ETF Summary Report.xlsx
+++ b/ETF Summary Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F37A6FAF-34A6-E54B-8021-B106CA181F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2337F239-8E35-AF4C-B6AC-7A5EF72323C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -158,9 +158,6 @@
     <t>MODEFENCE</t>
   </si>
   <si>
-    <t>Motilal Oswal MOSt Shares NASDAQ-100 ETF</t>
-  </si>
-  <si>
     <t>MON100</t>
   </si>
   <si>
@@ -240,6 +237,9 @@
   </si>
   <si>
     <t>ICICI Prudential Silver ETF</t>
+  </si>
+  <si>
+    <t>Motilal Oswal NASDAQ 100 ETF</t>
   </si>
 </sst>
 </file>
@@ -1777,16 +1777,16 @@
         <v>20</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="D20" s="5">
         <v>237</v>
       </c>
       <c r="E20" s="5">
-        <v>9.1199999999999992</v>
+        <v>184.68</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1794,10 +1794,10 @@
         <v>21</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="D21" s="5">
         <v>1938</v>
@@ -1811,10 +1811,10 @@
         <v>22</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>46</v>
       </c>
       <c r="D22" s="5">
         <v>409</v>
@@ -1828,10 +1828,10 @@
         <v>23</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>48</v>
       </c>
       <c r="D23" s="5">
         <v>1881</v>
@@ -1845,10 +1845,10 @@
         <v>24</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="D24" s="5">
         <v>148</v>
@@ -1862,10 +1862,10 @@
         <v>25</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="D25" s="5">
         <v>3812</v>
@@ -1879,10 +1879,10 @@
         <v>26</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>54</v>
       </c>
       <c r="D26" s="5">
         <v>868</v>
@@ -1896,10 +1896,10 @@
         <v>27</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>56</v>
       </c>
       <c r="D27" s="5">
         <v>2230</v>
@@ -1913,10 +1913,10 @@
         <v>28</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>58</v>
       </c>
       <c r="D28" s="5">
         <v>48</v>
@@ -1930,10 +1930,10 @@
         <v>30</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>60</v>
       </c>
       <c r="D29" s="5">
         <v>543</v>
@@ -1947,10 +1947,10 @@
         <v>31</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D30" s="5">
         <v>483</v>
@@ -1964,10 +1964,10 @@
         <v>32</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D31" s="5">
         <v>181</v>
@@ -1981,10 +1981,10 @@
         <v>33</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D32" s="5">
         <v>192</v>
@@ -1998,10 +1998,10 @@
         <v>34</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D33" s="5">
         <v>130</v>
